--- a/Books.xlsx
+++ b/Books.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5444515566c7376a/Documents/Programme/B4P/b4p-docu-maker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{B8246BD0-AB28-B246-8A82-ED27F370C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29C6342A-6231-466F-9A0B-E30C04AD7498}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B8246BD0-AB28-B246-8A82-ED27F370C745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9E9685-4D1D-4E6C-8980-63D585A51FBD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{3D6CAE77-ACA1-4461-B4A1-0A0F37C8EA4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D6CAE77-ACA1-4461-B4A1-0A0F37C8EA4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -134,13 +134,13 @@
     <t>Language Guide</t>
   </si>
   <si>
-    <t>Table Processing</t>
-  </si>
-  <si>
     <t>../georgzurbonsen.github.io/</t>
   </si>
   <si>
     <t>../Outputs/</t>
+  </si>
+  <si>
+    <t>Workflow</t>
   </si>
 </sst>
 </file>
@@ -623,7 +623,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -703,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -720,7 +720,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>12</v>
